--- a/Figure 6/Figure 6-B.xlsx
+++ b/Figure 6/Figure 6-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018F70AD-1CE9-4789-A883-46FB7778FB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30295A28-3228-4528-B55C-CB95E6A6CE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23970" yWindow="1110" windowWidth="19500" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,6 +76,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -98,9 +104,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -389,295 +396,296 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>0.28490028490028491</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>0.31054131054131057</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>0.25071225071225189</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>0.20797720797720914</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>0.22507122507122623</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>0.23789173789173906</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>0.35754985754985857</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>0.3703703703703714</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>0.24216524216524332</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>0.29772079772079874</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>0.19515669515669634</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>0.29344729344729448</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="1">
         <v>0.31481481481481582</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>0.37464387464387566</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="1">
         <v>0.27635327635327739</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="1">
         <v>0.30626780626780731</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="1">
         <v>0.18233618233618351</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="1">
         <v>0.23361823361823478</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="1">
         <v>0.3703703703703714</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="1">
         <v>0.35327635327635432</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="1">
         <v>0.19088319088319206</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="1">
         <v>0.20797720797720914</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="1">
         <v>0.21225071225071343</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="1">
         <v>0.23361823361823478</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="1">
         <v>0.26353276353276467</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="1">
         <v>0.39601139601139701</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="1">
         <v>0.57122507122507193</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="1">
         <v>0.40028490028490132</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="1">
         <v>0.30199430199430305</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="1">
         <v>0.38746438746438849</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="1">
         <v>0.10541310541310674</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="1">
         <v>0.23789173789173906</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="1">
         <v>0.16096866096866216</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="1">
         <v>0.21225071225071343</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="1">
         <v>0.16096866096866216</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="1">
         <v>0.16524216524216642</v>
       </c>
     </row>
